--- a/downloads/loesungen/06_Weiterbildung_2NF_Loesung.xlsx
+++ b/downloads/loesungen/06_Weiterbildung_2NF_Loesung.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURS" sheetId="1" r:id="Rfdc2c4f92c6e457e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DOZENT" sheetId="2" r:id="R38c528dd106f4556"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURS_DOZENT" sheetId="3" r:id="R16c0554b2d4747e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURS" sheetId="1" r:id="Ra7d1269d8a074c0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DOZENT" sheetId="2" r:id="Rfb83ee0873a9416d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KURS_DOZENT" sheetId="3" r:id="Rff1901a9b46a40b8"/>
   </x:sheets>
 </x:workbook>
 </file>
